--- a/src/rodos_corpus/data/corpus/rendered/finance/FIN-LIST-SOGL-RM-2027.xlsx
+++ b/src/rodos_corpus/data/corpus/rendered/finance/FIN-LIST-SOGL-RM-2027.xlsx
@@ -428,7 +428,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="53" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
@@ -496,7 +496,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.09.2026</t>
+          <t>23.09.2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -506,7 +506,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -541,12 +541,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>отсрочка 45 календарных дней сохранена; отмечено, что с 01.01.2027 исключение п. 5.3 регламента SALES-REGL-SKIDKI на договор не распространяется — договор заключён после даты утверждения регламента, и скидка заказчику перестаёт применяться</t>
+          <t>отсрочка 45 календарных дней сохранена в редакции РМ-2025/01; отмечено, что при таких условиях оплаты скидка по пункту 5.1 регламента SALES-REGL-SKIDKI не применяется, а исключение пункта 5.3 к договору не относится: оно сделано для условия «оплата по факту отгрузки», а у заказчика отсрочка платежа</t>
         </is>
       </c>
     </row>
@@ -566,7 +566,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>23.09.2026</t>
+          <t>24.09.2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -593,7 +593,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Начальник отдела снабжения</t>
+          <t>Коммерческий директор</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -611,7 +611,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>24.09.2026</t>
+          <t>25.09.2026</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -638,22 +638,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>подписано</t>
+          <t>не начато</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>25.09.2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>плановая сумма 7 400 000 ₽</t>
+          <t>плановая сумма 7 400 000 ₽; проект вступает в силу с 01.01.2027, к подписанию передаётся после согласования спецификаций СП-01 и СП-02 на 2027 год</t>
         </is>
       </c>
     </row>
